--- a/data/publications/monthly-rbi-bulletin/financial-markets/table-31-new-capital-issues-by-non-government-public-limited-companies.xlsx
+++ b/data/publications/monthly-rbi-bulletin/financial-markets/table-31-new-capital-issues-by-non-government-public-limited-companies.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="81">
   <si>
     <t>Security &amp; Type of Issue</t>
   </si>
@@ -419,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -475,6 +475,12 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="172" fontId="1" fillId="2" borderId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="1" fillId="2" borderId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
@@ -47658,7 +47664,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P29"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="10.06986" customWidth="1"/>
@@ -47776,435 +47782,435 @@
         <v>79</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D8" s="7">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E8" s="8">
-        <v>3905.23</v>
+        <v>19745.41</v>
       </c>
       <c r="F8" s="8">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="G8" s="8">
-        <v>2493.18</v>
+        <v>19237.2</v>
       </c>
       <c r="H8" s="8">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I8" s="8">
-        <v>1412.05</v>
+        <v>508.21</v>
       </c>
       <c r="J8" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" s="8">
-        <v>564.38</v>
+        <v>600</v>
       </c>
       <c r="L8" s="8">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="M8" s="8">
-        <v>4469.61</v>
+        <v>20345.41</v>
       </c>
       <c r="N8" s="8">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="O8" s="8">
-        <v>3057.56</v>
+        <v>19837.2</v>
       </c>
       <c r="P8" s="8">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="8">
-        <v>1412.05</v>
+        <v>508.21</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B9" s="9"/>
       <c r="C9" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="10">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E9" s="11">
-        <v>1860.65</v>
+        <v>2843.71</v>
       </c>
       <c r="F9" s="11">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G9" s="11">
-        <v>1576.63</v>
+        <v>2496.71</v>
       </c>
       <c r="H9" s="11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I9" s="11">
-        <v>284.02</v>
+        <v>347</v>
       </c>
       <c r="J9" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" s="11">
-        <v>746.2441</v>
+        <v>485.0783</v>
       </c>
       <c r="L9" s="11">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="M9" s="11">
-        <v>2606.8941</v>
+        <v>3328.7883</v>
       </c>
       <c r="N9" s="11">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O9" s="11">
-        <v>2322.8741</v>
+        <v>2981.7883</v>
       </c>
       <c r="P9" s="11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q9" s="11">
-        <v>284.02</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B10" s="9"/>
       <c r="C10" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" s="7">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E10" s="8">
-        <v>2843.71</v>
+        <v>1860.65</v>
       </c>
       <c r="F10" s="8">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G10" s="8">
-        <v>2496.71</v>
+        <v>1576.63</v>
       </c>
       <c r="H10" s="8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I10" s="8">
-        <v>347</v>
+        <v>284.02</v>
       </c>
       <c r="J10" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K10" s="8">
-        <v>485.0783</v>
+        <v>746.2441</v>
       </c>
       <c r="L10" s="8">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="M10" s="8">
-        <v>3328.7883</v>
+        <v>2606.8941</v>
       </c>
       <c r="N10" s="8">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="O10" s="8">
-        <v>2981.7883</v>
+        <v>2322.8741</v>
       </c>
       <c r="P10" s="8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q10" s="8">
-        <v>347</v>
+        <v>284.02</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="19.7321" customHeight="1">
-      <c r="B11" s="5" t="s">
-        <v>80</v>
-      </c>
+      <c r="B11" s="9"/>
       <c r="C11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="10">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E11" s="11">
-        <v>435.14</v>
+        <v>3905.23</v>
       </c>
       <c r="F11" s="11">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G11" s="11">
-        <v>254.86</v>
+        <v>2493.18</v>
       </c>
       <c r="H11" s="11">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I11" s="11">
-        <v>180.28</v>
+        <v>1412.05</v>
       </c>
       <c r="J11" s="11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K11" s="11">
-        <v>1276.85</v>
+        <v>564.38</v>
       </c>
       <c r="L11" s="11">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M11" s="11">
-        <v>1711.99</v>
+        <v>4469.61</v>
       </c>
       <c r="N11" s="11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O11" s="11">
-        <v>1531.71</v>
+        <v>3057.56</v>
       </c>
       <c r="P11" s="11">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="11">
-        <v>180.28</v>
+        <v>1412.05</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="19.7321" customHeight="1">
-      <c r="B12" s="9"/>
+      <c r="B12" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="C12" s="6" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D12" s="7">
+        <v>39</v>
+      </c>
+      <c r="E12" s="8">
+        <v>9924</v>
+      </c>
+      <c r="F12" s="8">
+        <v>20</v>
+      </c>
+      <c r="G12" s="8">
+        <v>8507</v>
+      </c>
+      <c r="H12" s="8">
         <v>19</v>
       </c>
-      <c r="E12" s="8">
-        <v>6756.562714</v>
-      </c>
-      <c r="F12" s="8">
-        <v>13</v>
-      </c>
-      <c r="G12" s="8">
-        <v>5683.8562</v>
-      </c>
-      <c r="H12" s="8">
-        <v>6</v>
-      </c>
       <c r="I12" s="8">
-        <v>1072.706514</v>
+        <v>1417</v>
       </c>
       <c r="J12" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12" s="8">
-        <v>575.62</v>
+        <v>1762.3497</v>
       </c>
       <c r="L12" s="8">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="M12" s="8">
-        <v>7332.182714</v>
+        <v>11686.3497</v>
       </c>
       <c r="N12" s="8">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="O12" s="8">
-        <v>6259.4762</v>
+        <v>10269.3497</v>
       </c>
       <c r="P12" s="8">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="Q12" s="8">
-        <v>1072.706514</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B13" s="9"/>
       <c r="C13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="10">
+        <v>24</v>
+      </c>
+      <c r="E13" s="11">
+        <v>4948.91</v>
+      </c>
+      <c r="F13" s="11">
+        <v>17</v>
+      </c>
+      <c r="G13" s="11">
+        <v>4649.91</v>
+      </c>
+      <c r="H13" s="11">
+        <v>7</v>
+      </c>
+      <c r="I13" s="11">
+        <v>299</v>
+      </c>
+      <c r="J13" s="11">
+        <v>3</v>
+      </c>
+      <c r="K13" s="11">
+        <v>895.87</v>
+      </c>
+      <c r="L13" s="11">
         <v>27</v>
       </c>
-      <c r="D13" s="10">
-        <v>40</v>
-      </c>
-      <c r="E13" s="11">
-        <v>15867.08377</v>
-      </c>
-      <c r="F13" s="11">
-        <v>24</v>
-      </c>
-      <c r="G13" s="11">
-        <v>9525.59422</v>
-      </c>
-      <c r="H13" s="11">
-        <v>16</v>
-      </c>
-      <c r="I13" s="11">
-        <v>6341.489552</v>
-      </c>
-      <c r="J13" s="11">
-        <v>2</v>
-      </c>
-      <c r="K13" s="11">
-        <v>233.34</v>
-      </c>
-      <c r="L13" s="11">
-        <v>42</v>
-      </c>
       <c r="M13" s="11">
-        <v>16100.42377</v>
+        <v>5844.78</v>
       </c>
       <c r="N13" s="11">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="O13" s="11">
-        <v>9758.93422</v>
+        <v>5545.78</v>
       </c>
       <c r="P13" s="11">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q13" s="11">
-        <v>6341.489552</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B14" s="9"/>
       <c r="C14" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="7">
+        <v>26</v>
+      </c>
+      <c r="E14" s="8">
+        <v>6093.7579016</v>
+      </c>
+      <c r="F14" s="8">
+        <v>18</v>
+      </c>
+      <c r="G14" s="8">
+        <v>5532.652072</v>
+      </c>
+      <c r="H14" s="8">
+        <v>8</v>
+      </c>
+      <c r="I14" s="8">
+        <v>561.1058296</v>
+      </c>
+      <c r="J14" s="8">
+        <v>2</v>
+      </c>
+      <c r="K14" s="8">
+        <v>1600.771819</v>
+      </c>
+      <c r="L14" s="8">
         <v>28</v>
       </c>
-      <c r="D14" s="7">
-        <v>59</v>
-      </c>
-      <c r="E14" s="8">
-        <v>28163.22667</v>
-      </c>
-      <c r="F14" s="8">
-        <v>45</v>
-      </c>
-      <c r="G14" s="8">
-        <v>26134.63381</v>
-      </c>
-      <c r="H14" s="8">
-        <v>14</v>
-      </c>
-      <c r="I14" s="8">
-        <v>2028.592858</v>
-      </c>
-      <c r="J14" s="8">
-        <v>7</v>
-      </c>
-      <c r="K14" s="8">
-        <v>2174.09</v>
-      </c>
-      <c r="L14" s="8">
-        <v>66</v>
-      </c>
       <c r="M14" s="8">
-        <v>30337.31667</v>
+        <v>7694.5297206</v>
       </c>
       <c r="N14" s="8">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="O14" s="8">
-        <v>28308.72381</v>
+        <v>7133.423891</v>
       </c>
       <c r="P14" s="8">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q14" s="8">
-        <v>2028.592858</v>
+        <v>561.1058296</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B15" s="9"/>
       <c r="C15" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D15" s="10">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E15" s="11">
-        <v>21545.48915</v>
+        <v>50516.21108</v>
       </c>
       <c r="F15" s="11">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G15" s="11">
-        <v>18261.29915</v>
+        <v>23553.09108</v>
       </c>
       <c r="H15" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I15" s="11">
-        <v>3284.19</v>
+        <v>26963.12</v>
       </c>
       <c r="J15" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="11">
-        <v>538.56</v>
+        <v>580.35</v>
       </c>
       <c r="L15" s="11">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="M15" s="11">
-        <v>22084.04915</v>
+        <v>51096.56108</v>
       </c>
       <c r="N15" s="11">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="O15" s="11">
-        <v>18799.85915</v>
+        <v>24133.44108</v>
       </c>
       <c r="P15" s="11">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q15" s="11">
-        <v>3284.19</v>
+        <v>26963.12</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B16" s="9"/>
       <c r="C16" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D16" s="7">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="E16" s="8">
-        <v>12914.25511</v>
+        <v>34875.112663</v>
       </c>
       <c r="F16" s="8">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="G16" s="8">
-        <v>11312.15146</v>
+        <v>33506.9</v>
       </c>
       <c r="H16" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I16" s="8">
-        <v>1602.103644</v>
+        <v>1368.212663</v>
       </c>
       <c r="J16" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="8">
-        <v>480.48</v>
+        <v>390.6077</v>
       </c>
       <c r="L16" s="8">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="M16" s="8">
-        <v>13394.73511</v>
+        <v>35265.720363</v>
       </c>
       <c r="N16" s="8">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="O16" s="8">
-        <v>11792.63146</v>
+        <v>33897.5077</v>
       </c>
       <c r="P16" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q16" s="8">
-        <v>1602.103644</v>
+        <v>1368.212663</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -48258,339 +48264,339 @@
     <row r="18" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B18" s="9"/>
       <c r="C18" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D18" s="7">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E18" s="8">
-        <v>34875.112663</v>
+        <v>12914.25511</v>
       </c>
       <c r="F18" s="8">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="G18" s="8">
-        <v>33506.9</v>
+        <v>11312.15146</v>
       </c>
       <c r="H18" s="8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I18" s="8">
-        <v>1368.212663</v>
+        <v>1602.103644</v>
       </c>
       <c r="J18" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18" s="8">
-        <v>390.6077</v>
+        <v>480.48</v>
       </c>
       <c r="L18" s="8">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="M18" s="8">
-        <v>35265.720363</v>
+        <v>13394.73511</v>
       </c>
       <c r="N18" s="8">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="O18" s="8">
-        <v>33897.5077</v>
+        <v>11792.63146</v>
       </c>
       <c r="P18" s="8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q18" s="8">
-        <v>1368.212663</v>
+        <v>1602.103644</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B19" s="9"/>
       <c r="C19" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D19" s="10">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E19" s="11">
-        <v>50516.21108</v>
+        <v>21545.48915</v>
       </c>
       <c r="F19" s="11">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G19" s="11">
-        <v>23553.09108</v>
+        <v>18261.29915</v>
       </c>
       <c r="H19" s="11">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I19" s="11">
-        <v>26963.12</v>
+        <v>3284.19</v>
       </c>
       <c r="J19" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" s="11">
-        <v>580.35</v>
+        <v>538.56</v>
       </c>
       <c r="L19" s="11">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="M19" s="11">
-        <v>51096.56108</v>
+        <v>22084.04915</v>
       </c>
       <c r="N19" s="11">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="O19" s="11">
-        <v>24133.44108</v>
+        <v>18799.85915</v>
       </c>
       <c r="P19" s="11">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q19" s="11">
-        <v>26963.12</v>
+        <v>3284.19</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B20" s="9"/>
       <c r="C20" s="6" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D20" s="7">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E20" s="8">
-        <v>6093.7579016</v>
+        <v>28163.22667</v>
       </c>
       <c r="F20" s="8">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="G20" s="8">
-        <v>5532.652072</v>
+        <v>26134.63381</v>
       </c>
       <c r="H20" s="8">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I20" s="8">
-        <v>561.1058296</v>
+        <v>2028.592858</v>
       </c>
       <c r="J20" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K20" s="8">
-        <v>1600.771819</v>
+        <v>2174.09</v>
       </c>
       <c r="L20" s="8">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="M20" s="8">
-        <v>7694.5297206</v>
+        <v>30337.31667</v>
       </c>
       <c r="N20" s="8">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="O20" s="8">
-        <v>7133.423891</v>
+        <v>28308.72381</v>
       </c>
       <c r="P20" s="8">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="8">
-        <v>561.1058296</v>
+        <v>2028.592858</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B21" s="9"/>
       <c r="C21" s="6" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D21" s="10">
+        <v>40</v>
+      </c>
+      <c r="E21" s="11">
+        <v>15867.08377</v>
+      </c>
+      <c r="F21" s="11">
         <v>24</v>
       </c>
-      <c r="E21" s="11">
-        <v>4948.91</v>
-      </c>
-      <c r="F21" s="11">
-        <v>17</v>
-      </c>
       <c r="G21" s="11">
-        <v>4649.91</v>
+        <v>9525.59422</v>
       </c>
       <c r="H21" s="11">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I21" s="11">
-        <v>299</v>
+        <v>6341.489552</v>
       </c>
       <c r="J21" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21" s="11">
-        <v>895.87</v>
+        <v>233.34</v>
       </c>
       <c r="L21" s="11">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="M21" s="11">
-        <v>5844.78</v>
+        <v>16100.42377</v>
       </c>
       <c r="N21" s="11">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O21" s="11">
-        <v>5545.78</v>
+        <v>9758.93422</v>
       </c>
       <c r="P21" s="11">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q21" s="11">
-        <v>299</v>
+        <v>6341.489552</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" ht="19.7321" customHeight="1">
       <c r="B22" s="9"/>
       <c r="C22" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D22" s="7">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E22" s="8">
-        <v>9924</v>
+        <v>6756.562714</v>
       </c>
       <c r="F22" s="8">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G22" s="8">
-        <v>8507</v>
+        <v>5683.8562</v>
       </c>
       <c r="H22" s="8">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I22" s="8">
-        <v>1417</v>
+        <v>1072.706514</v>
       </c>
       <c r="J22" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K22" s="8">
-        <v>1762.3497</v>
+        <v>575.62</v>
       </c>
       <c r="L22" s="8">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="M22" s="8">
-        <v>11686.3497</v>
+        <v>7332.182714</v>
       </c>
       <c r="N22" s="8">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="O22" s="8">
-        <v>10269.3497</v>
+        <v>6259.4762</v>
       </c>
       <c r="P22" s="8">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="Q22" s="8">
-        <v>1417</v>
+        <v>1072.706514</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="19.7321" customHeight="1">
-      <c r="B23" s="5" t="s">
-        <v>24</v>
-      </c>
+      <c r="B23" s="9"/>
       <c r="C23" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D23" s="10">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="E23" s="11">
-        <v>31118.61737</v>
+        <v>435.14</v>
       </c>
       <c r="F23" s="11">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="G23" s="11">
-        <v>27030.91</v>
+        <v>254.86</v>
       </c>
       <c r="H23" s="11">
+        <v>6</v>
+      </c>
+      <c r="I23" s="11">
+        <v>180.28</v>
+      </c>
+      <c r="J23" s="11">
+        <v>6</v>
+      </c>
+      <c r="K23" s="11">
+        <v>1276.85</v>
+      </c>
+      <c r="L23" s="11">
+        <v>20</v>
+      </c>
+      <c r="M23" s="11">
+        <v>1711.99</v>
+      </c>
+      <c r="N23" s="11">
         <v>14</v>
       </c>
-      <c r="I23" s="11">
-        <v>4087.71</v>
-      </c>
-      <c r="J23" s="11">
-        <v>4</v>
-      </c>
-      <c r="K23" s="11">
-        <v>806.01</v>
-      </c>
-      <c r="L23" s="11">
-        <v>52</v>
-      </c>
-      <c r="M23" s="11">
-        <v>31924.62737</v>
-      </c>
-      <c r="N23" s="11">
-        <v>38</v>
-      </c>
       <c r="O23" s="11">
-        <v>27836.92</v>
+        <v>1531.71</v>
       </c>
       <c r="P23" s="11">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q23" s="11">
-        <v>4087.71</v>
+        <v>180.28</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="19.7321" customHeight="1">
-      <c r="B24" s="9"/>
+      <c r="B24" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="C24" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D24" s="7">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E24" s="8">
-        <v>3620.490044</v>
+        <v>2038.770348</v>
       </c>
       <c r="F24" s="8">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="G24" s="8">
-        <v>3065.561367</v>
+        <v>530.53414</v>
       </c>
       <c r="H24" s="8">
+        <v>9</v>
+      </c>
+      <c r="I24" s="8">
+        <v>1508.236208</v>
+      </c>
+      <c r="J24" s="8">
+        <v>4</v>
+      </c>
+      <c r="K24" s="8">
+        <v>455</v>
+      </c>
+      <c r="L24" s="8">
+        <v>25</v>
+      </c>
+      <c r="M24" s="8">
+        <v>2493.770348</v>
+      </c>
+      <c r="N24" s="8">
         <v>16</v>
       </c>
-      <c r="I24" s="8">
-        <v>554.9286776</v>
-      </c>
-      <c r="J24" s="8">
-        <v>5</v>
-      </c>
-      <c r="K24" s="8">
-        <v>684.88</v>
-      </c>
-      <c r="L24" s="8">
-        <v>49</v>
-      </c>
-      <c r="M24" s="8">
-        <v>4305.370044</v>
-      </c>
-      <c r="N24" s="8">
-        <v>33</v>
-      </c>
       <c r="O24" s="8">
-        <v>3750.441367</v>
+        <v>985.53414</v>
       </c>
       <c r="P24" s="8">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="Q24" s="8">
-        <v>554.9286776</v>
+        <v>1508.236208</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="19.7321" customHeight="1">
@@ -48642,70 +48648,118 @@
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="19.7321" customHeight="1">
-      <c r="B26" s="12"/>
-      <c r="C26" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" s="14">
-        <v>21</v>
-      </c>
-      <c r="E26" s="15">
-        <v>2038.770348</v>
-      </c>
-      <c r="F26" s="15">
-        <v>12</v>
-      </c>
-      <c r="G26" s="15">
-        <v>530.53414</v>
-      </c>
-      <c r="H26" s="15">
-        <v>9</v>
-      </c>
-      <c r="I26" s="15">
-        <v>1508.236208</v>
-      </c>
-      <c r="J26" s="15">
+      <c r="B26" s="9"/>
+      <c r="C26" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="7">
+        <v>44</v>
+      </c>
+      <c r="E26" s="8">
+        <v>3620.490044</v>
+      </c>
+      <c r="F26" s="8">
+        <v>28</v>
+      </c>
+      <c r="G26" s="8">
+        <v>3065.561367</v>
+      </c>
+      <c r="H26" s="8">
+        <v>16</v>
+      </c>
+      <c r="I26" s="8">
+        <v>554.9286776</v>
+      </c>
+      <c r="J26" s="8">
+        <v>5</v>
+      </c>
+      <c r="K26" s="8">
+        <v>684.88</v>
+      </c>
+      <c r="L26" s="8">
+        <v>49</v>
+      </c>
+      <c r="M26" s="8">
+        <v>4305.370044</v>
+      </c>
+      <c r="N26" s="8">
+        <v>33</v>
+      </c>
+      <c r="O26" s="8">
+        <v>3750.441367</v>
+      </c>
+      <c r="P26" s="8">
+        <v>16</v>
+      </c>
+      <c r="Q26" s="8">
+        <v>554.9286776</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="19.7321" customHeight="1">
+      <c r="B27" s="12"/>
+      <c r="C27" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="19">
+        <v>48</v>
+      </c>
+      <c r="E27" s="20">
+        <v>31118.61737</v>
+      </c>
+      <c r="F27" s="20">
+        <v>34</v>
+      </c>
+      <c r="G27" s="20">
+        <v>27030.91</v>
+      </c>
+      <c r="H27" s="20">
+        <v>14</v>
+      </c>
+      <c r="I27" s="20">
+        <v>4087.71</v>
+      </c>
+      <c r="J27" s="20">
         <v>4</v>
       </c>
-      <c r="K26" s="15">
-        <v>455</v>
-      </c>
-      <c r="L26" s="15">
-        <v>25</v>
-      </c>
-      <c r="M26" s="15">
-        <v>2493.770348</v>
-      </c>
-      <c r="N26" s="15">
-        <v>16</v>
-      </c>
-      <c r="O26" s="15">
-        <v>985.53414</v>
-      </c>
-      <c r="P26" s="15">
-        <v>9</v>
-      </c>
-      <c r="Q26" s="15">
-        <v>1508.236208</v>
+      <c r="K27" s="20">
+        <v>806.01</v>
+      </c>
+      <c r="L27" s="20">
+        <v>52</v>
+      </c>
+      <c r="M27" s="20">
+        <v>31924.62737</v>
+      </c>
+      <c r="N27" s="20">
+        <v>38</v>
+      </c>
+      <c r="O27" s="20">
+        <v>27836.92</v>
+      </c>
+      <c r="P27" s="20">
+        <v>14</v>
+      </c>
+      <c r="Q27" s="20">
+        <v>4087.71</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
-    <row r="28" s="1" customFormat="1" ht="66.1292" customHeight="1">
-      <c r="B28" s="18" t="s">
+    <row r="28" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
+    <row r="29" s="1" customFormat="1" ht="66.1292" customHeight="1">
+      <c r="B29" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="B29:I29"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:E6"/>
